--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2537,6 +2537,112 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106822318</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89776</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ej möjlig att validera</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bornjöns Naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>657215</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6571336</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -1767,7 +1767,7 @@
         <v>106822318</v>
       </c>
       <c r="B11" t="n">
-        <v>90215</v>
+        <v>90225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -1767,7 +1767,7 @@
         <v>106822318</v>
       </c>
       <c r="B11" t="n">
-        <v>90225</v>
+        <v>90237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96871640</v>
+        <v>96958068</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657134.8631943403</v>
+        <v>657220</v>
       </c>
       <c r="R2" t="n">
-        <v>6571273.774946096</v>
+        <v>6571276</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,27 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>På starkt rötskadat rotben av gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,55 +783,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Ljungberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96872010</v>
+        <v>112128573</v>
       </c>
       <c r="B3" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657145.2432071457</v>
+        <v>657134</v>
       </c>
       <c r="R3" t="n">
-        <v>6571246.042584563</v>
+        <v>6571219</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,27 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,22 +884,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Ljungberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96871647</v>
+        <v>96871640</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657152.1250628063</v>
+        <v>657135</v>
       </c>
       <c r="R4" t="n">
-        <v>6571278.073244477</v>
+        <v>6571274</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,24 +962,14 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högstubbe av tall.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,37 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96871707</v>
+        <v>96957494</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>657153.1612514658</v>
+        <v>657190</v>
       </c>
       <c r="R5" t="n">
-        <v>6571253.026581023</v>
+        <v>6571254</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,27 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal tall i kanten mot kärr.</t>
+          <t>På granticka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,22 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Ljungberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96958117</v>
+        <v>106822319</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,40 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skansberg, Ö om, Srm</t>
+          <t>Bornjöns Naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657210.9006744248</v>
+        <v>657184</v>
       </c>
       <c r="R6" t="n">
-        <v>6571208.820397383</v>
+        <v>6571252</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,34 +1182,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Amelie Lindhagen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96957570</v>
+        <v>112128498</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1324,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>657204.3882563408</v>
+        <v>657134</v>
       </c>
       <c r="R7" t="n">
-        <v>6571254.634169219</v>
+        <v>6571271</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,22 +1272,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På granlåga. En del årsfärska dödade granar av granbarkborre. Gott om död ved i form av torrträd och lågor av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,15 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96957494</v>
+        <v>96958170</v>
       </c>
       <c r="B8" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,26 +1321,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1440,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657190.0294662096</v>
+        <v>657177</v>
       </c>
       <c r="R8" t="n">
-        <v>6571254.552008596</v>
+        <v>6571136</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1473,24 +1382,14 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granticka.</t>
+          <t>Vid roten av gammal tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96958068</v>
+        <v>112128627</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,35 +1428,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1570,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>657219.9278942415</v>
+        <v>657182</v>
       </c>
       <c r="R9" t="n">
-        <v>6571275.758575177</v>
+        <v>6571193</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1600,27 +1485,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På starkt rötskadat rotben av gran.</t>
+          <t>På nedre delen av torrgran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,53 +1523,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106822319</v>
+        <v>112128551</v>
       </c>
       <c r="B10" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bornjöns Naturreservat, Srm</t>
+          <t>Skansberg, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>657184.481426759</v>
+        <v>657162</v>
       </c>
       <c r="R10" t="n">
-        <v>6571252.274301577</v>
+        <v>6571271</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,22 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,75 +1605,70 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Bornsjön</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106822318</v>
+        <v>96871647</v>
       </c>
       <c r="B11" t="n">
-        <v>90237</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256756</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bornjöns Naturreservat, Srm</t>
+          <t>Skansberg, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657215</v>
+        <v>657152</v>
       </c>
       <c r="R11" t="n">
-        <v>6571336</v>
+        <v>6571278</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,12 +1692,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,37 +1711,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Bornsjön</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Bo Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112128551</v>
+        <v>112128530</v>
       </c>
       <c r="B12" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1913,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657162</v>
+        <v>657144</v>
       </c>
       <c r="R12" t="n">
-        <v>6571271</v>
+        <v>6571278</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1949,6 +1804,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,15 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112128573</v>
+        <v>96871707</v>
       </c>
       <c r="B13" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657134</v>
+        <v>657153</v>
       </c>
       <c r="R13" t="n">
-        <v>6571219</v>
+        <v>6571253</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2049,12 +1904,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal tall i kanten mot kärr.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,44 +1935,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Ljungberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112128627</v>
+        <v>96957570</v>
       </c>
       <c r="B14" t="n">
-        <v>90274</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657182</v>
+        <v>657204</v>
       </c>
       <c r="R14" t="n">
-        <v>6571192</v>
+        <v>6571255</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,17 +2010,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På nedre delen av torrgran.</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,37 +2043,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112128530</v>
+        <v>96958117</v>
       </c>
       <c r="B15" t="n">
-        <v>89989</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657144</v>
+        <v>657211</v>
       </c>
       <c r="R15" t="n">
-        <v>6571278</v>
+        <v>6571209</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,17 +2111,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På högstubbe av tall.</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,16 +2147,11 @@
         <v>112128708</v>
       </c>
       <c r="B16" t="n">
-        <v>90874</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2329,12 +2164,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2355,7 +2190,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657216</v>
+        <v>657217</v>
       </c>
       <c r="R16" t="n">
         <v>6571313</v>
@@ -2418,15 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112128498</v>
+        <v>121934865</v>
       </c>
       <c r="B17" t="n">
-        <v>90205</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,40 +2264,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansberg, Ö om, Srm</t>
+          <t>Kaspersdal, Kaspersdal, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657134</v>
+        <v>657114</v>
       </c>
       <c r="R17" t="n">
-        <v>6571271</v>
+        <v>6571262</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,17 +2323,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På granlåga. En del årsfärska dödade granar av granbarkborre. Gott om död ved i form av torrträd och lågor av gran.</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,22 +2347,447 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96872010</v>
+      </c>
+      <c r="B18" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>657146</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6571246</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnag- och kläckhål i fnöskticka på högstubbe av björk.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96958272</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>657224</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6571207</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnagspår på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
         <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>106822092</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bornjöns Naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>657154</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6571173</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen, David Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>106822318</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bornjöns Naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>657215</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6571336</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43913-2021 artfynd.xlsx
+++ b/artfynd/A 43913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96958068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128573</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96957494</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Bornsjön</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822319</t>
         </is>
       </c>
     </row>
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128498</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96958170</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128627</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871647</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871707</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2040,6 +2105,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96957570</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96958117</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128708</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121934865</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96872010</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96958272</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822092</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2788,8 +2888,35 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>